--- a/sample-data/pos-minmax-main-kitchen.xlsx
+++ b/sample-data/pos-minmax-main-kitchen.xlsx
@@ -430,13 +430,13 @@
         <v>kg</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -450,13 +450,13 @@
         <v>kg</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -470,13 +470,13 @@
         <v>ltr</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -490,13 +490,13 @@
         <v>kg</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,13 @@
         <v>kg</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -530,13 +530,13 @@
         <v>btl</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         <v>btl</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>14</v>
@@ -570,13 +570,13 @@
         <v>pkt</v>
       </c>
       <c r="D9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -610,7 +610,7 @@
         <v>kg</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -650,13 +650,13 @@
         <v>kg</v>
       </c>
       <c r="D13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -670,13 +670,13 @@
         <v>kg</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -690,13 +690,13 @@
         <v>pc</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -710,13 +710,13 @@
         <v>kg</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -730,13 +730,13 @@
         <v>kg</v>
       </c>
       <c r="D17">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -750,13 +750,13 @@
         <v>kg</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -770,13 +770,13 @@
         <v>pc</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -790,13 +790,13 @@
         <v>pkt</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -813,10 +813,10 @@
         <v>4</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -830,13 +830,13 @@
         <v>ltr</v>
       </c>
       <c r="D22">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -850,13 +850,13 @@
         <v>kg</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="F23">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -870,13 +870,13 @@
         <v>kg</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -890,13 +890,13 @@
         <v>pkt</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/sample-data/pos-minmax-main-kitchen.xlsx
+++ b/sample-data/pos-minmax-main-kitchen.xlsx
@@ -430,13 +430,13 @@
         <v>kg</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -450,13 +450,13 @@
         <v>kg</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -470,13 +470,13 @@
         <v>ltr</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -490,13 +490,13 @@
         <v>kg</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -510,13 +510,13 @@
         <v>kg</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -530,13 +530,13 @@
         <v>btl</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -550,13 +550,13 @@
         <v>btl</v>
       </c>
       <c r="D8">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>2</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -570,13 +570,13 @@
         <v>pkt</v>
       </c>
       <c r="D9">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -590,13 +590,13 @@
         <v>kg</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -610,10 +610,10 @@
         <v>kg</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -630,13 +630,13 @@
         <v>kg</v>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>kg</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -670,13 +670,13 @@
         <v>kg</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -690,13 +690,13 @@
         <v>pc</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -710,13 +710,13 @@
         <v>kg</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>3</v>
       </c>
       <c r="F16">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -730,13 +730,13 @@
         <v>kg</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -750,13 +750,13 @@
         <v>kg</v>
       </c>
       <c r="D18">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -770,13 +770,13 @@
         <v>pc</v>
       </c>
       <c r="D19">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -790,13 +790,13 @@
         <v>pkt</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -810,13 +810,13 @@
         <v>roll</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -830,13 +830,13 @@
         <v>ltr</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -850,13 +850,13 @@
         <v>kg</v>
       </c>
       <c r="D23">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -870,10 +870,10 @@
         <v>kg</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24">
         <v>5</v>
@@ -893,10 +893,10 @@
         <v>4</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
